--- a/src/cubes/data/housing_stock/energy-system-schema.xlsx
+++ b/src/cubes/data/housing_stock/energy-system-schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JackLynch/CUBES/exp/jack/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/housing_stock/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549CDAE0-A3BA-6C4B-95FC-4D1413543083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649B2A4F-3EC4-1B43-B18A-6EA7D244B110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1960" yWindow="460" windowWidth="25040" windowHeight="13440" xr2:uid="{4DAF8F1F-FDB7-8C42-B032-28677CD2A744}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25040" windowHeight="13440" xr2:uid="{4DAF8F1F-FDB7-8C42-B032-28677CD2A744}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,10 +137,10 @@
     <t>Individual gas condensing boiler</t>
   </si>
   <si>
-    <t>Ambience</t>
-  </si>
-  <si>
     <t>EnergyPlus</t>
+  </si>
+  <si>
+    <t>HEATING SYSTEM 1 TECHNOLOGY</t>
   </si>
 </sst>
 </file>
@@ -525,10 +525,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
